--- a/BOM/PSFB_MCU_BOM_29.06.2026_EN.xlsx
+++ b/BOM/PSFB_MCU_BOM_29.06.2026_EN.xlsx
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>DS1073-01-2x1-MVT6</t>
+          <t>DS1073-01-2x1MR2T6</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>DS1073-01-2x2-MVT6</t>
+          <t>DS1073-01-2x2MR2T6</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr"/>
